--- a/public/templates/procore-line-items-template.xlsx
+++ b/public/templates/procore-line-items-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ToddGilmore\Analytics\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39B08EA-953A-4732-9C9F-E7F7461D2EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB1AE3C-174E-4C1B-8D7D-D64FA44D1600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LineItems" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="38">
   <si>
     <t>name</t>
   </si>
@@ -34,12 +34,24 @@
     <t>labor_factor</t>
   </si>
   <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>item_cost</t>
+  </si>
+  <si>
+    <t>labor_cost</t>
+  </si>
+  <si>
     <t>tag</t>
   </si>
   <si>
     <t>ci_type</t>
   </si>
   <si>
+    <t>ci_item_id</t>
+  </si>
+  <si>
     <t>ci_name</t>
   </si>
   <si>
@@ -103,7 +115,7 @@
     <t>ci_color</t>
   </si>
   <si>
-    <t>Concrete - 4000 PSI</t>
+    <t>Winter Concrete</t>
   </si>
   <si>
     <t>Concrete - Foundations</t>
@@ -112,25 +124,13 @@
     <t/>
   </si>
   <si>
-    <t>PART</t>
-  </si>
-  <si>
-    <t>Ready-mix concrete</t>
-  </si>
-  <si>
-    <t>CY</t>
-  </si>
-  <si>
-    <t>Local Ready Mix Co.</t>
-  </si>
-  <si>
-    <t>ABC Supply</t>
-  </si>
-  <si>
-    <t>Standard 4000 PSI mix</t>
-  </si>
-  <si>
-    <t>03-300</t>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>Use during winter months only for added Concrete cost of Material</t>
+  </si>
+  <si>
+    <t>ea</t>
   </si>
   <si>
     <t>hrs</t>
@@ -510,39 +510,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="19" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="56.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -624,94 +628,213 @@
       <c r="AA1" t="s">
         <v>26</v>
       </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>15528361</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
-        <v>27</v>
+      <c r="E2">
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>155</v>
+      </c>
+      <c r="G2">
+        <v>14.4</v>
       </c>
       <c r="H2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2">
+        <v>51482284</v>
+      </c>
+      <c r="K2" t="s">
         <v>31</v>
       </c>
-      <c r="I2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2">
+      <c r="L2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2">
         <v>155</v>
       </c>
-      <c r="K2">
+      <c r="O2">
         <v>12</v>
       </c>
-      <c r="L2" t="s">
+      <c r="P2" t="s">
         <v>37</v>
       </c>
-      <c r="M2">
+      <c r="Q2">
         <v>14.4</v>
       </c>
-      <c r="N2">
+      <c r="R2">
         <v>72</v>
       </c>
-      <c r="O2">
+      <c r="S2">
         <v>0.05</v>
       </c>
-      <c r="P2">
+      <c r="T2">
         <v>0.03</v>
       </c>
-      <c r="Q2">
+      <c r="U2">
         <v>0.1</v>
       </c>
-      <c r="R2">
+      <c r="V2">
         <v>0.12</v>
       </c>
-      <c r="S2" t="b">
+      <c r="W2" t="b">
         <v>0</v>
       </c>
-      <c r="T2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W2" t="s">
-        <v>29</v>
-      </c>
       <c r="X2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y2">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>33</v>
       </c>
       <c r="Z2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="AA2" t="s">
-        <v>29</v>
+        <v>33</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R3" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AA1 A2:K2 V2:AA2 M2:T2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AE1 A3:AE3 A2:D2 F2:AE2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>